--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,40 +28,67 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20019631</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK 1L</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20037153</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 250</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 250</t>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGGA 245ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20140328</t>
+  </si>
+  <si>
+    <t>BUAVITA K MS.GRP 245</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -454,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -540,15 +567,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -557,10 +584,70 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,64 +31,55 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20037153</t>
-  </si>
-  <si>
-    <t>KAKI3 PENYEGAR 500ML</t>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
+    <t>20094164</t>
+  </si>
+  <si>
+    <t>MIZONE ACTIVE 500ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGGA 245ML</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU SL 245</t>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>20140328</t>
-  </si>
-  <si>
-    <t>BUAVITA K MS.GRP 245</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -481,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -547,15 +538,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -564,10 +555,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,15 +578,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -604,18 +595,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -624,30 +615,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t/>
   </si>
   <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
+    <t>20019631</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK 1L</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,52 +31,49 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
     <t>6</t>
@@ -578,15 +575,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,18 +592,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -615,10 +612,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>20019631</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK 1L</t>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,55 +28,67 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20076052</t>
+  </si>
+  <si>
+    <t>PUCUK TEH MLTI 1.3L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>10004906</t>
   </si>
   <si>
     <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -469,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -535,15 +547,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -552,10 +564,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -575,15 +587,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -592,18 +604,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -612,10 +624,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
   <si>
-    <t>10000426</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL1500</t>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,10 +31,10 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20076052</t>
-  </si>
-  <si>
-    <t>PUCUK TEH MLTI 1.3L</t>
+    <t>20139359</t>
+  </si>
+  <si>
+    <t>KIT KAT CHO KLG 220</t>
   </si>
   <si>
     <t>2</t>
@@ -43,52 +43,25 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
+    <t>20135340</t>
+  </si>
+  <si>
+    <t>MILO DRNK EXT.CHO220</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
+    <t>10014404</t>
+  </si>
+  <si>
+    <t>MILO HEALTY DRINK220</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>RT,(E-2B)</t>
   </si>
 </sst>
 </file>
@@ -481,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -590,66 +563,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,40 +28,61 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20139359</t>
-  </si>
-  <si>
-    <t>KIT KAT CHO KLG 220</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20037153</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135340</t>
-  </si>
-  <si>
-    <t>MILO DRNK EXT.CHO220</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10014404</t>
-  </si>
-  <si>
-    <t>MILO HEALTY DRINK220</t>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20115188</t>
+  </si>
+  <si>
+    <t>CMORY UHT ALMND 250</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20122822</t>
+  </si>
+  <si>
+    <t>CMORY UHT MARIE 250</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -454,13 +475,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -540,7 +561,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,6 +582,46 @@
       </c>
       <c r="F5" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t/>
   </si>
   <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,58 +31,61 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20037153</t>
-  </si>
-  <si>
-    <t>KAKI3 PENYEGAR 500ML</t>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGGA 245ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>20139578</t>
   </si>
   <si>
     <t>PC GOLDN CARAMEL 210</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20115188</t>
-  </si>
-  <si>
-    <t>CMORY UHT ALMND 250</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20122822</t>
-  </si>
-  <si>
-    <t>CMORY UHT MARIE 250</t>
-  </si>
-  <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -475,13 +478,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -541,15 +544,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -558,7 +561,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -566,10 +569,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -578,18 +581,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -598,18 +601,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -618,10 +621,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,61 +31,55 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU SL 245</t>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGGA 245ML</t>
+    <t>20094167</t>
+  </si>
+  <si>
+    <t>MIZONE MOOD UP 500</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MATCHA LATTEA 330</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -478,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -564,15 +558,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -581,10 +575,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,15 +598,15 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -621,30 +615,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t/>
   </si>
   <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,58 +28,70 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -472,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -538,15 +550,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -555,18 +567,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -575,18 +587,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,18 +607,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -615,10 +627,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t/>
   </si>
   <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,70 +28,52 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
+    <t>20002205</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA BLKCR500</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
+    <t>20002203</t>
+  </si>
+  <si>
+    <t>SOSRO F.TEA APEL 500</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
+    <t>20134046</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 500</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -484,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -550,15 +532,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -567,18 +549,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -587,18 +569,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -607,18 +589,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -627,30 +609,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200ML</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,49 +31,70 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20002205</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA BLKCR500</t>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20002203</t>
-  </si>
-  <si>
-    <t>SOSRO F.TEA APEL 500</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20134046</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 500</t>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGGA 245ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -466,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -552,35 +573,35 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -589,18 +610,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -609,9 +630,49 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 200ML</t>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,73 +28,49 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT200</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
+    <t>20129102</t>
+  </si>
+  <si>
+    <t>OATSDE BR.BLEND 200</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
+    <t>20129123</t>
+  </si>
+  <si>
+    <t>OATSDE CHOCO 200</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU SL 245</t>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGGA 245ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>RT,(E-3B)</t>
   </si>
 </sst>
 </file>
@@ -487,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -553,15 +529,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -570,10 +546,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -593,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -613,67 +589,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t/>
   </si>
   <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,49 +28,70 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20129102</t>
-  </si>
-  <si>
-    <t>OATSDE BR.BLEND 200</t>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20129123</t>
-  </si>
-  <si>
-    <t>OATSDE CHOCO 200</t>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -463,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -529,67 +550,127 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600 ML</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,67 +31,46 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT F CRM 946 ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535 G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535 G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 LECI 320 ML</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>RT,(E-4B)</t>
   </si>
 </sst>
 </file>
@@ -484,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -570,15 +549,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -587,18 +566,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -607,70 +586,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t/>
   </si>
   <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600 ML</t>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,46 +31,52 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT F CRM 946 ML</t>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535 G</t>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535 G</t>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 LECI 320 ML</t>
+    <t>20046319</t>
+  </si>
+  <si>
+    <t>PANDA GRASS JELY310</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20141495</t>
+  </si>
+  <si>
+    <t>PANDA GRN GRS JEL310</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -463,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -549,15 +555,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -566,18 +572,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -586,10 +592,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,49 +31,49 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
+    <t>10005909</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT PLN 950</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20046319</t>
-  </si>
-  <si>
-    <t>PANDA GRASS JELY310</t>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20141495</t>
-  </si>
-  <si>
-    <t>PANDA GRN GRS JEL310</t>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGGA 245ML</t>
   </si>
   <si>
     <t>6</t>
@@ -555,15 +555,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -572,18 +572,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -592,10 +592,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
+    <t>20142239</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 1L</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,52 +31,64 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10005909</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT PLN 950</t>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
+    <t>20122061</t>
+  </si>
+  <si>
+    <t>OATSDE O/M B/BLND 1L</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU SL 245</t>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGGA 245ML</t>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -469,16 +481,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +510,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -514,11 +533,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -534,11 +553,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -554,16 +573,16 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -572,13 +591,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -594,11 +613,11 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -614,8 +633,28 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20142239</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 1L</t>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,67 +28,58 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20036200</t>
+  </si>
+  <si>
+    <t>SPRITE SOFT DRINK 1L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20122061</t>
-  </si>
-  <si>
-    <t>OATSDE O/M B/BLND 1L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -481,17 +472,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,14 +500,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -533,11 +517,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -553,16 +537,16 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -571,18 +555,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -591,18 +575,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -611,18 +595,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -631,30 +615,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>22</v>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t/>
   </si>
   <si>
-    <t>10000426</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL1500</t>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -31,16 +31,28 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20036200</t>
-  </si>
-  <si>
-    <t>SPRITE SOFT DRINK 1L</t>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20035484</t>
@@ -49,7 +61,7 @@
     <t>PUCUK/H TEH MLATI350</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -61,22 +73,13 @@
     <t>PUCUK/H TEH L/SGR350</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KURMA SUSU KR189</t>
   </si>
   <si>
     <t>6</t>
@@ -478,7 +481,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -578,15 +581,15 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,18 +598,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -615,10 +618,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,61 +28,46 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20056219</t>
+  </si>
+  <si>
+    <t>ETERNALPLUS BTL 500</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20142495</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN 1L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
 </sst>
 </file>
@@ -475,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -541,15 +526,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -558,18 +543,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -578,18 +563,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -598,30 +583,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
